--- a/web/public/forms/orig/o-jajae-seungin.xlsx
+++ b/web/public/forms/orig/o-jajae-seungin.xlsx
@@ -636,7 +636,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1288,7 +1288,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="30" t="inlineStr">

--- a/web/public/forms/orig/o-jajae-seungin.xlsx
+++ b/web/public/forms/orig/o-jajae-seungin.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="승인요청" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시-승인요청" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'승인요청'!$A$1:$L$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'예시-승인요청'!$A$1:$L$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -163,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -247,9 +245,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -713,10 +708,7 @@
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="10" t="n"/>
       <c r="D7" s="6" t="n"/>
-      <c r="E7" s="11">
-        <f>"건축"&amp;IF(C7="건축","■","□")&amp;"   "&amp;"기계"&amp;IF(C7="기계","■","□")&amp;"   "&amp;"토목"&amp;IF(C7="토목","■","□")&amp;"   "&amp;"기타"&amp;IF(C7="기타","■","□")</f>
-        <v/>
-      </c>
+      <c r="E7" s="11" t="n"/>
       <c r="F7" s="6" t="n"/>
       <c r="G7" s="6" t="n"/>
       <c r="H7" s="6" t="n"/>
@@ -881,10 +873,7 @@
           <t>공장등록증</t>
         </is>
       </c>
-      <c r="K12" s="17">
-        <f>IF(COUNTIF(C12:I13,"■")=0,"","첨부 "&amp;COUNTIF(C12:I13,"■")&amp;"종")</f>
-        <v/>
-      </c>
+      <c r="K12" s="17" t="n"/>
       <c r="L12" s="6" t="n"/>
     </row>
     <row r="13" ht="24" customHeight="1">
@@ -1050,10 +1039,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n"/>
-      <c r="C25" s="26">
-        <f>IF(C6="","",C6&amp;IF(C8="",""," — "&amp;C8&amp;IF(I8="",""," ("&amp;I8&amp;")")))</f>
-        <v/>
-      </c>
+      <c r="C25" s="26" t="n"/>
       <c r="D25" s="6" t="n"/>
       <c r="E25" s="6" t="n"/>
       <c r="F25" s="6" t="n"/>
@@ -1091,10 +1077,7 @@
       <c r="B27" s="6" t="n"/>
       <c r="C27" s="10" t="n"/>
       <c r="D27" s="6" t="n"/>
-      <c r="E27" s="11">
-        <f>"적합"&amp;IF(C27="적합","■","□")&amp;"   "&amp;"조건부적합"&amp;IF(C27="조건부적합","■","□")&amp;"   "&amp;"부적합"&amp;IF(C27="부적합","■","□")</f>
-        <v/>
-      </c>
+      <c r="E27" s="11" t="n"/>
       <c r="F27" s="6" t="n"/>
       <c r="G27" s="6" t="n"/>
       <c r="H27" s="6" t="n"/>
@@ -1104,10 +1087,7 @@
       <c r="L27" s="6" t="n"/>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="27">
-        <f>IF(C27="부적합","⚠ 부적합 — 다른 공급원으로 다시 요청해야 합니다.",IF(C27="조건부적합","※ 조건부적합 — 조건(특기사항)을 지켜 쓰고 결과를 보고합니다.",""))</f>
-        <v/>
-      </c>
+      <c r="A28" s="27" t="n"/>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
@@ -1175,718 +1155,11 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36" ht="19.5" customHeight="1">
       <c r="A36" s="29" t="inlineStr">
         <is>
           <t>□ 칸은 목록에서 ■ 를 고르세요. 하늘색 칸 = 자동(공종·판정 표시 · 첨부 수 · 통보서 공사명).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="59">
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="I8:L8"/>
-    <mergeCell ref="K12:L13"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C11:L11"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A32:L32"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="C6:L6"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C14:L14"/>
-    <mergeCell ref="A20:L20"/>
-    <mergeCell ref="G1:L1"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="A19:L19"/>
-    <mergeCell ref="C26:L26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="C29:L29"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="E27:L27"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="E7:L7"/>
-    <mergeCell ref="C9:L9"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="A36:L36"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="I5:L5"/>
-  </mergeCells>
-  <dataValidations count="3">
-    <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"건축,기계,토목,기타"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C10 C12 C13 E10 E12 E13 G10 G12 G13 I10 I12 I13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"□,■"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"적합,조건부적합,부적합"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.5" right="0.5" top="0.45" bottom="0.45" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:L36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="7.6" customWidth="1" min="1" max="1"/>
-    <col width="7.6" customWidth="1" min="2" max="2"/>
-    <col width="7.6" customWidth="1" min="3" max="3"/>
-    <col width="7.6" customWidth="1" min="4" max="4"/>
-    <col width="7.6" customWidth="1" min="5" max="5"/>
-    <col width="7.6" customWidth="1" min="6" max="6"/>
-    <col width="7.6" customWidth="1" min="7" max="7"/>
-    <col width="7.6" customWidth="1" min="8" max="8"/>
-    <col width="7.6" customWidth="1" min="9" max="9"/>
-    <col width="7.6" customWidth="1" min="10" max="10"/>
-    <col width="7.6" customWidth="1" min="11" max="11"/>
-    <col width="7.6" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="G1" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>[별지 제37호 서식]</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>자재 공급원 승인 요청 · 결과통보 내용</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="4" customHeight="1"/>
-    <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>문서번호</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>예시건설 제2026-045호</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>수    신</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>책임건설사업관리기술인</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="n"/>
-      <c r="K5" s="6" t="n"/>
-      <c r="L5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>공 사 명</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>가나지구 배수로 정비공사</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>공    종</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>토목</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="11">
-        <f>"건축"&amp;IF(C7="건축","■","□")&amp;"   "&amp;"기계"&amp;IF(C7="기계","■","□")&amp;"   "&amp;"토목"&amp;IF(C7="토목","■","□")&amp;"   "&amp;"기타"&amp;IF(C7="기타","■","□")</f>
-        <v/>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>품    명</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>PC 암거</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>규    격</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>1.5m × 1.5m × 1.0m</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>제조회사명</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>예시콘크리트(주)</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>KS · 녹색제품
-유무</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>KS</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="F10" s="14" t="inlineStr">
-        <is>
-          <t>비KS</t>
-        </is>
-      </c>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>환경표지</t>
-        </is>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="J10" s="14" t="inlineStr">
-        <is>
-          <t>GR</t>
-        </is>
-      </c>
-      <c r="K10" s="15" t="inlineStr"/>
-      <c r="L10" s="6" t="n"/>
-    </row>
-    <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>시공자 의견</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>설계도서의 규격(KS F 4413)과 같고 납품 실적이 충분하여 공급원으로 승인을 요청합니다.</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="6" t="n"/>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>첨    부</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>인증서</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>사업자등록증</t>
-        </is>
-      </c>
-      <c r="G12" s="13" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="I12" s="13" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
-        <is>
-          <t>공장등록증</t>
-        </is>
-      </c>
-      <c r="K12" s="17">
-        <f>IF(COUNTIF(C12:I13,"■")=0,"","첨부 "&amp;COUNTIF(C12:I13,"■")&amp;"종")</f>
-        <v/>
-      </c>
-      <c r="L12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="6" t="n"/>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>시험성적서</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>납품실적</t>
-        </is>
-      </c>
-      <c r="G13" s="13" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>견본</t>
-        </is>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="J13" s="16" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>특기사항</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>시험성적서는 공인시험기관 발행분(최근 6개월 이내)</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-      <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="6" t="n"/>
-    </row>
-    <row r="15" ht="6" customHeight="1"/>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="18" t="inlineStr"/>
-      <c r="F16" s="19" t="inlineStr">
-        <is>
-          <t>담  당  자</t>
-        </is>
-      </c>
-      <c r="I16" s="20" t="inlineStr">
-        <is>
-          <t>이공무</t>
-        </is>
-      </c>
-      <c r="L16" s="21" t="inlineStr">
-        <is>
-          <t>(인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="18" t="inlineStr"/>
-      <c r="F17" s="19" t="inlineStr">
-        <is>
-          <t>현장대리인</t>
-        </is>
-      </c>
-      <c r="I17" s="20" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="L17" s="21" t="inlineStr">
-        <is>
-          <t>(인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="4" customHeight="1"/>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="22" t="inlineStr">
-        <is>
-          <t>상기 자재에 대한 검토를 요청하오니 결과를 통보하여 주시기 바랍니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="23" t="n">
-        <v>46114</v>
-      </c>
-    </row>
-    <row r="21" ht="8" customHeight="1">
-      <c r="A21" s="24" t="n"/>
-      <c r="B21" s="24" t="n"/>
-      <c r="C21" s="24" t="n"/>
-      <c r="D21" s="24" t="n"/>
-      <c r="E21" s="24" t="n"/>
-      <c r="F21" s="24" t="n"/>
-      <c r="G21" s="24" t="n"/>
-      <c r="H21" s="24" t="n"/>
-      <c r="I21" s="24" t="n"/>
-      <c r="J21" s="24" t="n"/>
-      <c r="K21" s="24" t="n"/>
-      <c r="L21" s="24" t="n"/>
-    </row>
-    <row r="22" ht="6" customHeight="1"/>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="25" t="inlineStr">
-        <is>
-          <t>자재승인 검토결과 통보서</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>문서번호</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>가나감리 제2026-112호</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="6" t="n"/>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>수    신</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="n"/>
-      <c r="I24" s="10" t="inlineStr">
-        <is>
-          <t>현장대리인</t>
-        </is>
-      </c>
-      <c r="J24" s="6" t="n"/>
-      <c r="K24" s="6" t="n"/>
-      <c r="L24" s="6" t="n"/>
-    </row>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>공사명 · 품명</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="26">
-        <f>IF(C6="","",C6&amp;IF(C8="",""," — "&amp;C8&amp;IF(I8="",""," ("&amp;I8&amp;")")))</f>
-        <v/>
-      </c>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="n"/>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="n"/>
-      <c r="I25" s="6" t="n"/>
-      <c r="J25" s="6" t="n"/>
-      <c r="K25" s="6" t="n"/>
-      <c r="L25" s="6" t="n"/>
-    </row>
-    <row r="26" ht="48" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>검토 의견</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>제출 서류 확인 결과 설계도서 규격과 같고 품질관리 체계가 적정함.</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
-      <c r="I26" s="6" t="n"/>
-      <c r="J26" s="6" t="n"/>
-      <c r="K26" s="6" t="n"/>
-      <c r="L26" s="6" t="n"/>
-    </row>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>판    정</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>적합</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="11">
-        <f>"적합"&amp;IF(C27="적합","■","□")&amp;"   "&amp;"조건부적합"&amp;IF(C27="조건부적합","■","□")&amp;"   "&amp;"부적합"&amp;IF(C27="부적합","■","□")</f>
-        <v/>
-      </c>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
-      <c r="I27" s="6" t="n"/>
-      <c r="J27" s="6" t="n"/>
-      <c r="K27" s="6" t="n"/>
-      <c r="L27" s="6" t="n"/>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="27">
-        <f>IF(C27="부적합","⚠ 부적합 — 다른 공급원으로 다시 요청해야 합니다.",IF(C27="조건부적합","※ 조건부적합 — 조건(특기사항)을 지켜 쓰고 결과를 보고합니다.",""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="36" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>특기사항</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="28" t="inlineStr">
-        <is>
-          <t>1. 공장방문 후 검토결과를 통보할 경우 해당 공장방문 검사 Check List 첨부
-2. 자체시험 및 외부 의뢰시험을 실시하는 경우 시험 결과치 기록 또는 시험성적서 첨부</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="n"/>
-      <c r="G29" s="6" t="n"/>
-      <c r="H29" s="6" t="n"/>
-      <c r="I29" s="6" t="n"/>
-      <c r="J29" s="6" t="n"/>
-      <c r="K29" s="6" t="n"/>
-      <c r="L29" s="6" t="n"/>
-    </row>
-    <row r="30" ht="4" customHeight="1"/>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="22" t="inlineStr">
-        <is>
-          <t>상기 검토요청에 대한 검토결과를 통보합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="23" t="n">
-        <v>46118</v>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="18" t="inlineStr"/>
-      <c r="F33" s="19" t="inlineStr">
-        <is>
-          <t>담당 건설사업관리기술인</t>
-        </is>
-      </c>
-      <c r="I33" s="20" t="inlineStr">
-        <is>
-          <t>김철수</t>
-        </is>
-      </c>
-      <c r="L33" s="21" t="inlineStr">
-        <is>
-          <t>(인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="18" t="inlineStr"/>
-      <c r="F34" s="19" t="inlineStr">
-        <is>
-          <t>책임건설사업관리기술인</t>
-        </is>
-      </c>
-      <c r="I34" s="20" t="inlineStr">
-        <is>
-          <t>박책임</t>
-        </is>
-      </c>
-      <c r="L34" s="21" t="inlineStr">
-        <is>
-          <t>(인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="19.5" customHeight="1">
-      <c r="A36" s="29" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 공사 · 회사 · 사람).</t>
         </is>
       </c>
     </row>

--- a/web/public/forms/orig/o-jajae-seungin.xlsx
+++ b/web/public/forms/orig/o-jajae-seungin.xlsx
@@ -631,7 +631,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
